--- a/data/cruceta.xlsx
+++ b/data/cruceta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,20 +457,40 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>05dec2025</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>06dec2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>07dec2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>08dec2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -495,15 +515,27 @@
         <v>4</v>
       </c>
       <c r="F2" t="n">
+        <v>28</v>
+      </c>
+      <c r="G2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" t="n">
+        <v>14</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
         <v>16</v>
       </c>
-      <c r="G2" t="n">
+      <c r="K2" t="n">
         <v>22</v>
       </c>
-      <c r="H2" t="n">
+      <c r="L2" t="n">
         <v>24</v>
       </c>
-      <c r="I2" t="n">
+      <c r="M2" t="n">
         <v>15</v>
       </c>
     </row>
@@ -526,15 +558,27 @@
         <v>4</v>
       </c>
       <c r="F3" t="n">
+        <v>23</v>
+      </c>
+      <c r="G3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H3" t="n">
+        <v>14</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
         <v>15</v>
       </c>
-      <c r="G3" t="n">
+      <c r="K3" t="n">
         <v>19</v>
       </c>
-      <c r="H3" t="n">
+      <c r="L3" t="n">
         <v>25</v>
       </c>
-      <c r="I3" t="n">
+      <c r="M3" t="n">
         <v>17</v>
       </c>
     </row>
@@ -557,15 +601,27 @@
         <v>5</v>
       </c>
       <c r="F4" t="n">
+        <v>23</v>
+      </c>
+      <c r="G4" t="n">
+        <v>15</v>
+      </c>
+      <c r="H4" t="n">
+        <v>21</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
         <v>17</v>
       </c>
-      <c r="G4" t="n">
+      <c r="K4" t="n">
         <v>18</v>
       </c>
-      <c r="H4" t="n">
+      <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" t="n">
+      <c r="M4" t="n">
         <v>38</v>
       </c>
     </row>
@@ -588,15 +644,27 @@
         <v>5</v>
       </c>
       <c r="F5" t="n">
+        <v>27</v>
+      </c>
+      <c r="G5" t="n">
+        <v>16</v>
+      </c>
+      <c r="H5" t="n">
+        <v>12</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
         <v>20</v>
       </c>
-      <c r="G5" t="n">
+      <c r="K5" t="n">
         <v>25</v>
       </c>
-      <c r="H5" t="n">
+      <c r="L5" t="n">
         <v>19</v>
       </c>
-      <c r="I5" t="n">
+      <c r="M5" t="n">
         <v>15</v>
       </c>
     </row>
@@ -619,15 +687,27 @@
         <v>3</v>
       </c>
       <c r="F6" t="n">
+        <v>28</v>
+      </c>
+      <c r="G6" t="n">
         <v>15</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
+        <v>12</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>15</v>
+      </c>
+      <c r="K6" t="n">
         <v>20</v>
       </c>
-      <c r="H6" t="n">
+      <c r="L6" t="n">
         <v>22</v>
       </c>
-      <c r="I6" t="n">
+      <c r="M6" t="n">
         <v>25</v>
       </c>
     </row>
@@ -650,15 +730,27 @@
         <v>5</v>
       </c>
       <c r="F7" t="n">
+        <v>23</v>
+      </c>
+      <c r="G7" t="n">
+        <v>15</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>14</v>
+      </c>
+      <c r="J7" t="n">
         <v>20</v>
       </c>
-      <c r="G7" t="n">
+      <c r="K7" t="n">
         <v>22</v>
       </c>
-      <c r="H7" t="n">
+      <c r="L7" t="n">
         <v>20</v>
       </c>
-      <c r="I7" t="n">
+      <c r="M7" t="n">
         <v>15</v>
       </c>
     </row>
@@ -681,15 +773,27 @@
         <v>7</v>
       </c>
       <c r="F8" t="n">
+        <v>17</v>
+      </c>
+      <c r="G8" t="n">
+        <v>18</v>
+      </c>
+      <c r="H8" t="n">
+        <v>18</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
         <v>15</v>
       </c>
-      <c r="G8" t="n">
+      <c r="K8" t="n">
         <v>17</v>
       </c>
-      <c r="H8" t="n">
+      <c r="L8" t="n">
         <v>30</v>
       </c>
-      <c r="I8" t="n">
+      <c r="M8" t="n">
         <v>18</v>
       </c>
     </row>
@@ -712,15 +816,27 @@
         <v>5</v>
       </c>
       <c r="F9" t="n">
+        <v>17</v>
+      </c>
+      <c r="G9" t="n">
+        <v>10</v>
+      </c>
+      <c r="H9" t="n">
+        <v>12</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
         <v>21</v>
       </c>
-      <c r="G9" t="n">
+      <c r="K9" t="n">
         <v>21</v>
       </c>
-      <c r="H9" t="n">
+      <c r="L9" t="n">
         <v>21</v>
       </c>
-      <c r="I9" t="n">
+      <c r="M9" t="n">
         <v>15</v>
       </c>
     </row>
@@ -743,15 +859,27 @@
         <v>5</v>
       </c>
       <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>36</v>
+      </c>
+      <c r="H10" t="n">
+        <v>9</v>
+      </c>
+      <c r="I10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J10" t="n">
         <v>17</v>
       </c>
-      <c r="G10" t="n">
+      <c r="K10" t="n">
         <v>19</v>
       </c>
-      <c r="H10" t="n">
+      <c r="L10" t="n">
         <v>15</v>
       </c>
-      <c r="I10" t="n">
+      <c r="M10" t="n">
         <v>15</v>
       </c>
     </row>
@@ -774,15 +902,27 @@
         <v>8</v>
       </c>
       <c r="F11" t="n">
+        <v>18</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>18</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
         <v>20</v>
       </c>
-      <c r="G11" t="n">
+      <c r="K11" t="n">
         <v>17</v>
       </c>
-      <c r="H11" t="n">
+      <c r="L11" t="n">
         <v>19</v>
       </c>
-      <c r="I11" t="n">
+      <c r="M11" t="n">
         <v>16</v>
       </c>
     </row>
@@ -797,7 +937,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -828,20 +968,40 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>05dec2025</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>06dec2025</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>07dec2025</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>08dec2025</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -875,20 +1035,36 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -922,20 +1098,36 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -969,16 +1161,32 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
         <is>
           <t>38</t>
         </is>
@@ -1012,20 +1220,36 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1059,20 +1283,36 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -1106,20 +1346,36 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1153,20 +1409,36 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1200,20 +1472,36 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1245,22 +1533,38 @@
           <t>5</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1294,20 +1598,32 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>16</t>
         </is>

--- a/data/cruceta.xlsx
+++ b/data/cruceta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,20 +477,30 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>09dec2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>10dec2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -524,18 +534,24 @@
         <v>14</v>
       </c>
       <c r="I2" t="n">
+        <v>16</v>
+      </c>
+      <c r="J2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>16</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>22</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>24</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>15</v>
       </c>
     </row>
@@ -567,18 +583,24 @@
         <v>14</v>
       </c>
       <c r="I3" t="n">
+        <v>15</v>
+      </c>
+      <c r="J3" t="n">
+        <v>19</v>
+      </c>
+      <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>15</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>19</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>25</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>17</v>
       </c>
     </row>
@@ -610,18 +632,24 @@
         <v>21</v>
       </c>
       <c r="I4" t="n">
+        <v>9</v>
+      </c>
+      <c r="J4" t="n">
+        <v>16</v>
+      </c>
+      <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>17</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>18</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>0</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>38</v>
       </c>
     </row>
@@ -653,18 +681,24 @@
         <v>12</v>
       </c>
       <c r="I5" t="n">
+        <v>11</v>
+      </c>
+      <c r="J5" t="n">
+        <v>13</v>
+      </c>
+      <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>20</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>25</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>19</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>15</v>
       </c>
     </row>
@@ -696,18 +730,24 @@
         <v>12</v>
       </c>
       <c r="I6" t="n">
+        <v>8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>11</v>
+      </c>
+      <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>15</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>20</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>22</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>25</v>
       </c>
     </row>
@@ -739,18 +779,24 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="J7" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K7" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>20</v>
       </c>
       <c r="M7" t="n">
+        <v>22</v>
+      </c>
+      <c r="N7" t="n">
+        <v>20</v>
+      </c>
+      <c r="O7" t="n">
         <v>15</v>
       </c>
     </row>
@@ -782,18 +828,24 @@
         <v>18</v>
       </c>
       <c r="I8" t="n">
+        <v>17</v>
+      </c>
+      <c r="J8" t="n">
+        <v>19</v>
+      </c>
+      <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>15</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>17</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>30</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>18</v>
       </c>
     </row>
@@ -825,18 +877,24 @@
         <v>12</v>
       </c>
       <c r="I9" t="n">
+        <v>9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>14</v>
+      </c>
+      <c r="K9" t="n">
         <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>21</v>
-      </c>
-      <c r="K9" t="n">
-        <v>21</v>
       </c>
       <c r="L9" t="n">
         <v>21</v>
       </c>
       <c r="M9" t="n">
+        <v>21</v>
+      </c>
+      <c r="N9" t="n">
+        <v>21</v>
+      </c>
+      <c r="O9" t="n">
         <v>15</v>
       </c>
     </row>
@@ -868,18 +926,24 @@
         <v>9</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="J10" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" t="n">
         <v>17</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>19</v>
       </c>
-      <c r="L10" t="n">
+      <c r="N10" t="n">
         <v>15</v>
       </c>
-      <c r="M10" t="n">
+      <c r="O10" t="n">
         <v>15</v>
       </c>
     </row>
@@ -911,18 +975,24 @@
         <v>18</v>
       </c>
       <c r="I11" t="n">
+        <v>14</v>
+      </c>
+      <c r="J11" t="n">
+        <v>16</v>
+      </c>
+      <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>20</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>17</v>
       </c>
-      <c r="L11" t="n">
+      <c r="N11" t="n">
         <v>19</v>
       </c>
-      <c r="M11" t="n">
+      <c r="O11" t="n">
         <v>16</v>
       </c>
     </row>
@@ -937,7 +1007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -988,20 +1058,30 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>09dec2025</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>10dec2025</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1048,23 +1128,33 @@
           <t>14</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1111,23 +1201,33 @@
           <t>14</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -1174,19 +1274,29 @@
           <t>21</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
         <is>
           <t>38</t>
         </is>
@@ -1233,23 +1343,33 @@
           <t>12</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1296,23 +1416,33 @@
           <t>12</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -1357,25 +1487,31 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1422,23 +1558,33 @@
           <t>18</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1485,23 +1631,33 @@
           <t>12</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1546,25 +1702,35 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1607,23 +1773,33 @@
           <t>18</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>16</t>
         </is>

--- a/data/cruceta.xlsx
+++ b/data/cruceta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,20 +487,25 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>11dec2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -540,18 +545,21 @@
         <v>12</v>
       </c>
       <c r="K2" t="n">
+        <v>13</v>
+      </c>
+      <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>16</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>22</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>24</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>15</v>
       </c>
     </row>
@@ -589,18 +597,21 @@
         <v>19</v>
       </c>
       <c r="K3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>15</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>19</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>25</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>17</v>
       </c>
     </row>
@@ -638,18 +649,21 @@
         <v>16</v>
       </c>
       <c r="K4" t="n">
+        <v>13</v>
+      </c>
+      <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>17</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>18</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>38</v>
       </c>
     </row>
@@ -687,18 +701,21 @@
         <v>13</v>
       </c>
       <c r="K5" t="n">
+        <v>12</v>
+      </c>
+      <c r="L5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>20</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>25</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>19</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>15</v>
       </c>
     </row>
@@ -736,18 +753,21 @@
         <v>11</v>
       </c>
       <c r="K6" t="n">
+        <v>11</v>
+      </c>
+      <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>15</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>20</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>22</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>25</v>
       </c>
     </row>
@@ -785,18 +805,21 @@
         <v>9</v>
       </c>
       <c r="K7" t="n">
+        <v>12</v>
+      </c>
+      <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>20</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>22</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>20</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>15</v>
       </c>
     </row>
@@ -834,18 +857,21 @@
         <v>19</v>
       </c>
       <c r="K8" t="n">
+        <v>15</v>
+      </c>
+      <c r="L8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>15</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>17</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>30</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>18</v>
       </c>
     </row>
@@ -883,10 +909,10 @@
         <v>14</v>
       </c>
       <c r="K9" t="n">
+        <v>20</v>
+      </c>
+      <c r="L9" t="n">
         <v>0</v>
-      </c>
-      <c r="L9" t="n">
-        <v>21</v>
       </c>
       <c r="M9" t="n">
         <v>21</v>
@@ -895,6 +921,9 @@
         <v>21</v>
       </c>
       <c r="O9" t="n">
+        <v>21</v>
+      </c>
+      <c r="P9" t="n">
         <v>15</v>
       </c>
     </row>
@@ -935,17 +964,20 @@
         <v>5</v>
       </c>
       <c r="L10" t="n">
+        <v>7</v>
+      </c>
+      <c r="M10" t="n">
         <v>17</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>19</v>
-      </c>
-      <c r="N10" t="n">
-        <v>15</v>
       </c>
       <c r="O10" t="n">
         <v>15</v>
       </c>
+      <c r="P10" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -981,18 +1013,21 @@
         <v>16</v>
       </c>
       <c r="K11" t="n">
+        <v>15</v>
+      </c>
+      <c r="L11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>20</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>17</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>19</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1007,7 +1042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1068,20 +1103,25 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>11dec2025</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1138,23 +1178,28 @@
           <t>12</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1211,23 +1256,28 @@
           <t>19</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -1284,19 +1334,24 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
         <is>
           <t>38</t>
         </is>
@@ -1353,23 +1408,28 @@
           <t>13</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1426,23 +1486,28 @@
           <t>11</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -1495,23 +1560,28 @@
           <t>9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1568,23 +1638,28 @@
           <t>19</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1641,23 +1716,28 @@
           <t>14</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1717,20 +1797,25 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1783,23 +1868,28 @@
           <t>16</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>16</t>
         </is>

--- a/data/cruceta.xlsx
+++ b/data/cruceta.xlsx
@@ -548,7 +548,7 @@
         <v>13</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="M2" t="n">
         <v>16</v>
@@ -600,7 +600,7 @@
         <v>10</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M3" t="n">
         <v>15</v>
@@ -652,7 +652,7 @@
         <v>13</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M4" t="n">
         <v>17</v>
@@ -704,7 +704,7 @@
         <v>12</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M5" t="n">
         <v>20</v>
@@ -756,7 +756,7 @@
         <v>11</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M6" t="n">
         <v>15</v>
@@ -808,7 +808,7 @@
         <v>12</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M7" t="n">
         <v>20</v>
@@ -860,7 +860,7 @@
         <v>15</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M8" t="n">
         <v>15</v>
@@ -912,7 +912,7 @@
         <v>20</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M9" t="n">
         <v>21</v>
@@ -964,7 +964,7 @@
         <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="M10" t="n">
         <v>17</v>
@@ -1016,7 +1016,7 @@
         <v>15</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="M11" t="n">
         <v>20</v>
@@ -1183,7 +1183,11 @@
           <t>13</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
           <t>16</t>
@@ -1261,7 +1265,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>15</t>
@@ -1339,7 +1347,11 @@
           <t>13</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>17</t>
@@ -1413,7 +1425,11 @@
           <t>12</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>20</t>
@@ -1491,7 +1507,11 @@
           <t>11</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>15</t>
@@ -1565,7 +1585,11 @@
           <t>12</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>20</t>
@@ -1643,7 +1667,11 @@
           <t>15</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
           <t>15</t>
@@ -1721,7 +1749,11 @@
           <t>20</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>21</t>
@@ -1797,7 +1829,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>18</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1873,7 +1905,11 @@
           <t>15</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>20</t>

--- a/data/cruceta.xlsx
+++ b/data/cruceta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -492,20 +492,35 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>12dec2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>13dec2025</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14dec2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -551,15 +566,24 @@
         <v>13</v>
       </c>
       <c r="M2" t="n">
+        <v>24</v>
+      </c>
+      <c r="N2" t="n">
+        <v>9</v>
+      </c>
+      <c r="O2" t="n">
+        <v>5</v>
+      </c>
+      <c r="P2" t="n">
         <v>16</v>
       </c>
-      <c r="N2" t="n">
+      <c r="Q2" t="n">
         <v>22</v>
       </c>
-      <c r="O2" t="n">
+      <c r="R2" t="n">
         <v>24</v>
       </c>
-      <c r="P2" t="n">
+      <c r="S2" t="n">
         <v>15</v>
       </c>
     </row>
@@ -603,15 +627,24 @@
         <v>12</v>
       </c>
       <c r="M3" t="n">
+        <v>22</v>
+      </c>
+      <c r="N3" t="n">
+        <v>5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>4</v>
+      </c>
+      <c r="P3" t="n">
         <v>15</v>
       </c>
-      <c r="N3" t="n">
+      <c r="Q3" t="n">
         <v>19</v>
       </c>
-      <c r="O3" t="n">
+      <c r="R3" t="n">
         <v>25</v>
       </c>
-      <c r="P3" t="n">
+      <c r="S3" t="n">
         <v>17</v>
       </c>
     </row>
@@ -655,15 +688,24 @@
         <v>12</v>
       </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>21</v>
+      </c>
+      <c r="O4" t="n">
+        <v>13</v>
+      </c>
+      <c r="P4" t="n">
         <v>17</v>
       </c>
-      <c r="N4" t="n">
+      <c r="Q4" t="n">
         <v>18</v>
       </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
         <v>0</v>
       </c>
-      <c r="P4" t="n">
+      <c r="S4" t="n">
         <v>38</v>
       </c>
     </row>
@@ -707,15 +749,24 @@
         <v>12</v>
       </c>
       <c r="M5" t="n">
+        <v>24</v>
+      </c>
+      <c r="N5" t="n">
+        <v>10</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3</v>
+      </c>
+      <c r="P5" t="n">
         <v>20</v>
       </c>
-      <c r="N5" t="n">
+      <c r="Q5" t="n">
         <v>25</v>
       </c>
-      <c r="O5" t="n">
+      <c r="R5" t="n">
         <v>19</v>
       </c>
-      <c r="P5" t="n">
+      <c r="S5" t="n">
         <v>15</v>
       </c>
     </row>
@@ -759,15 +810,24 @@
         <v>11</v>
       </c>
       <c r="M6" t="n">
+        <v>24</v>
+      </c>
+      <c r="N6" t="n">
+        <v>9</v>
+      </c>
+      <c r="O6" t="n">
+        <v>14</v>
+      </c>
+      <c r="P6" t="n">
         <v>15</v>
       </c>
-      <c r="N6" t="n">
+      <c r="Q6" t="n">
         <v>20</v>
       </c>
-      <c r="O6" t="n">
+      <c r="R6" t="n">
         <v>22</v>
       </c>
-      <c r="P6" t="n">
+      <c r="S6" t="n">
         <v>25</v>
       </c>
     </row>
@@ -811,15 +871,24 @@
         <v>11</v>
       </c>
       <c r="M7" t="n">
+        <v>19</v>
+      </c>
+      <c r="N7" t="n">
+        <v>5</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2</v>
+      </c>
+      <c r="P7" t="n">
         <v>20</v>
       </c>
-      <c r="N7" t="n">
+      <c r="Q7" t="n">
         <v>22</v>
       </c>
-      <c r="O7" t="n">
+      <c r="R7" t="n">
         <v>20</v>
       </c>
-      <c r="P7" t="n">
+      <c r="S7" t="n">
         <v>15</v>
       </c>
     </row>
@@ -863,15 +932,24 @@
         <v>14</v>
       </c>
       <c r="M8" t="n">
+        <v>11</v>
+      </c>
+      <c r="N8" t="n">
+        <v>8</v>
+      </c>
+      <c r="O8" t="n">
+        <v>14</v>
+      </c>
+      <c r="P8" t="n">
         <v>15</v>
       </c>
-      <c r="N8" t="n">
+      <c r="Q8" t="n">
         <v>17</v>
       </c>
-      <c r="O8" t="n">
+      <c r="R8" t="n">
         <v>30</v>
       </c>
-      <c r="P8" t="n">
+      <c r="S8" t="n">
         <v>18</v>
       </c>
     </row>
@@ -918,12 +996,21 @@
         <v>21</v>
       </c>
       <c r="N9" t="n">
+        <v>8</v>
+      </c>
+      <c r="O9" t="n">
+        <v>7</v>
+      </c>
+      <c r="P9" t="n">
         <v>21</v>
       </c>
-      <c r="O9" t="n">
+      <c r="Q9" t="n">
         <v>21</v>
       </c>
-      <c r="P9" t="n">
+      <c r="R9" t="n">
+        <v>21</v>
+      </c>
+      <c r="S9" t="n">
         <v>15</v>
       </c>
     </row>
@@ -967,7 +1054,7 @@
         <v>18</v>
       </c>
       <c r="M10" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="N10" t="n">
         <v>19</v>
@@ -976,6 +1063,15 @@
         <v>15</v>
       </c>
       <c r="P10" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>19</v>
+      </c>
+      <c r="R10" t="n">
+        <v>15</v>
+      </c>
+      <c r="S10" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1019,15 +1115,24 @@
         <v>14</v>
       </c>
       <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>19</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5</v>
+      </c>
+      <c r="P11" t="n">
         <v>20</v>
       </c>
-      <c r="N11" t="n">
+      <c r="Q11" t="n">
         <v>17</v>
       </c>
-      <c r="O11" t="n">
+      <c r="R11" t="n">
         <v>19</v>
       </c>
-      <c r="P11" t="n">
+      <c r="S11" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1042,7 +1147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1108,20 +1213,35 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
+          <t>12dec2025</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>13dec2025</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>14dec2025</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1190,20 +1310,35 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1272,20 +1407,35 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -1352,18 +1502,29 @@
           <t>12</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr">
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
         <is>
           <t>38</t>
         </is>
@@ -1432,20 +1593,35 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1514,20 +1690,35 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -1592,20 +1783,35 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1674,20 +1880,35 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1761,15 +1982,30 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1834,20 +2070,35 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1910,22 +2161,33 @@
           <t>14</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>16</t>
         </is>

--- a/data/cruceta.xlsx
+++ b/data/cruceta.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,20 +507,25 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>15dec2025</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -575,15 +580,18 @@
         <v>5</v>
       </c>
       <c r="P2" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q2" t="n">
         <v>16</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>22</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>24</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>15</v>
       </c>
     </row>
@@ -636,15 +644,18 @@
         <v>4</v>
       </c>
       <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>15</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>19</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>25</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>17</v>
       </c>
     </row>
@@ -697,15 +708,18 @@
         <v>13</v>
       </c>
       <c r="P4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q4" t="n">
         <v>17</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>18</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>0</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>38</v>
       </c>
     </row>
@@ -758,15 +772,18 @@
         <v>3</v>
       </c>
       <c r="P5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q5" t="n">
         <v>20</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>25</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>19</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>15</v>
       </c>
     </row>
@@ -819,15 +836,18 @@
         <v>14</v>
       </c>
       <c r="P6" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q6" t="n">
         <v>15</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>20</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>22</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>25</v>
       </c>
     </row>
@@ -880,15 +900,18 @@
         <v>2</v>
       </c>
       <c r="P7" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q7" t="n">
         <v>20</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>22</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>20</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>15</v>
       </c>
     </row>
@@ -941,15 +964,18 @@
         <v>14</v>
       </c>
       <c r="P8" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q8" t="n">
         <v>15</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>17</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>30</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>18</v>
       </c>
     </row>
@@ -1002,7 +1028,7 @@
         <v>7</v>
       </c>
       <c r="P9" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="n">
         <v>21</v>
@@ -1011,6 +1037,9 @@
         <v>21</v>
       </c>
       <c r="S9" t="n">
+        <v>21</v>
+      </c>
+      <c r="T9" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1063,15 +1092,18 @@
         <v>15</v>
       </c>
       <c r="P10" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q10" t="n">
         <v>17</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>19</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>15</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1124,15 +1156,18 @@
         <v>5</v>
       </c>
       <c r="P11" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q11" t="n">
         <v>20</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>17</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>19</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>16</v>
       </c>
     </row>
@@ -1147,7 +1182,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1228,20 +1263,25 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
+          <t>15dec2025</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
           <t>27nov2025</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>28nov2025</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>29nov2025</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>30nov2025</t>
         </is>
@@ -1325,20 +1365,25 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1420,22 +1465,23 @@
           <t>4</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>17</t>
         </is>
@@ -1515,16 +1561,21 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr">
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
         <is>
           <t>38</t>
         </is>
@@ -1608,20 +1659,25 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1705,20 +1761,25 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>25</t>
         </is>
@@ -1798,20 +1859,25 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -1895,20 +1961,25 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>18</t>
         </is>
@@ -1992,20 +2063,25 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -2085,20 +2161,25 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -2174,20 +2255,25 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>16</t>
         </is>
